--- a/data/trans_camb/P15A-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,46</t>
+          <t>-1,38; 1,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,7</t>
+          <t>-1,05; 1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,64</t>
+          <t>-1,31; 1,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,16</t>
+          <t>-1,59; 1,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,72</t>
+          <t>-0,75; 2,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,29</t>
+          <t>0,21; 3,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,89</t>
+          <t>-1,22; 0,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,83</t>
+          <t>-0,54; 1,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,27</t>
+          <t>-0,0; 2,12</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,32; 82,59</t>
+          <t>-46,36; 92,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 102,24</t>
+          <t>-36,05; 110,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 98,23</t>
+          <t>-44,77; 85,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 42,15</t>
+          <t>-38,57; 38,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 94,03</t>
+          <t>-19,09; 92,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 118,4</t>
+          <t>4,4; 122,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 36,34</t>
+          <t>-33,83; 36,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 69,65</t>
+          <t>-15,71; 72,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 91,52</t>
+          <t>-0,99; 81,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; -0,12</t>
+          <t>-2,93; -0,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,63</t>
+          <t>-3,31; -0,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -1,25</t>
+          <t>-3,96; -1,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,12</t>
+          <t>-0,89; 1,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,35</t>
+          <t>-1,59; 0,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,66</t>
+          <t>-1,46; 0,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,06</t>
+          <t>-1,55; 0,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,6</t>
+          <t>-2,13; -0,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; -0,7</t>
+          <t>-2,36; -0,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,68; -2,28</t>
+          <t>-52,55; -2,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,75; -14,83</t>
+          <t>-60,95; -18,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,7; -30,87</t>
+          <t>-73,17; -30,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 67,8</t>
+          <t>-32,7; 66,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,29; 25,16</t>
+          <t>-57,6; 18,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 41,33</t>
+          <t>-51,25; 39,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,53; 2,26</t>
+          <t>-39,66; 3,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,5; -19,33</t>
+          <t>-54,63; -18,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,54; -22,57</t>
+          <t>-59,34; -21,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,54</t>
+          <t>-3,25; 1,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,91</t>
+          <t>-3,56; 0,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,12</t>
+          <t>-3,87; 0,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,97</t>
+          <t>-1,92; 3,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,71</t>
+          <t>-2,44; 1,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,38</t>
+          <t>-3,08; 0,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,63</t>
+          <t>-1,8; 1,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,76</t>
+          <t>-2,36; 0,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,1</t>
+          <t>-2,96; -0,2</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,79; 69,62</t>
+          <t>-64,93; 81,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 48,28</t>
+          <t>-74,45; 50,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-83,6; 15,16</t>
+          <t>-80,17; 22,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 159,3</t>
+          <t>-53,13; 187,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 103,09</t>
+          <t>-61,35; 93,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 26,17</t>
+          <t>-69,98; 33,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 77,97</t>
+          <t>-45,61; 72,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 34,69</t>
+          <t>-58,04; 26,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,26; 2,95</t>
+          <t>-71,6; -5,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,03</t>
+          <t>-1,79; -0,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,27</t>
+          <t>-2,1; -0,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,81</t>
+          <t>-2,59; -0,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,81</t>
+          <t>-0,83; 0,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,51</t>
+          <t>-1,08; 0,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,48</t>
+          <t>-1,07; 0,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,15</t>
+          <t>-1,03; 0,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,12</t>
+          <t>-1,29; -0,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; -0,32</t>
+          <t>-1,56; -0,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 1,02</t>
+          <t>-42,39; 0,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,57; -7,56</t>
+          <t>-49,8; -8,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,97; -24,08</t>
+          <t>-61,24; -22,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 36,43</t>
+          <t>-26,17; 32,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 22,14</t>
+          <t>-33,78; 22,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 19,85</t>
+          <t>-34,17; 21,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 4,88</t>
+          <t>-29,46; 6,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,95; -4,01</t>
+          <t>-35,44; -3,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,17; -10,91</t>
+          <t>-43,85; -12,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15A-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>0,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,56</t>
+          <t>-1,46; 1,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,92</t>
+          <t>-1,12; 1,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,48</t>
+          <t>-1,43; 1,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,1</t>
+          <t>-1,6; 1,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,61</t>
+          <t>-0,86; 2,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,36</t>
+          <t>0,02; 3,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,95</t>
+          <t>-1,1; 0,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,78</t>
+          <t>-0,48; 1,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 2,12</t>
+          <t>-0,18; 1,97</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>-4,14%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 92,73</t>
+          <t>-49,44; 75,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 110,85</t>
+          <t>-37,73; 97,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 85,05</t>
+          <t>-48,67; 84,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 38,69</t>
+          <t>-38,19; 48,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 92,14</t>
+          <t>-22,46; 90,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 122,36</t>
+          <t>-0,63; 117,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 36,56</t>
+          <t>-31,52; 35,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 72,21</t>
+          <t>-13,92; 67,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 81,51</t>
+          <t>-5,77; 78,92</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>-2,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-1,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,2</t>
+          <t>-2,9; -0,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; -0,72</t>
+          <t>-3,36; -0,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; -1,27</t>
+          <t>-3,47; -0,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,11</t>
+          <t>-0,93; 1,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,25</t>
+          <t>-1,57; 0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,64</t>
+          <t>-1,04; 0,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,1</t>
+          <t>-1,58; 0,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; -0,58</t>
+          <t>-2,25; -0,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; -0,66</t>
+          <t>-2,02; -0,37</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-54,53%</t>
+          <t>-46,38%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-17,09%</t>
+          <t>-7,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,06%</t>
+          <t>-34,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,55; -2,18</t>
+          <t>-52,9; -6,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,95; -18,01</t>
+          <t>-61,11; -21,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,17; -30,79</t>
+          <t>-64,59; -22,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 66,76</t>
+          <t>-34,22; 66,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,6; 18,24</t>
+          <t>-56,36; 19,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 39,7</t>
+          <t>-39,96; 46,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 3,91</t>
+          <t>-40,28; 1,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,63; -18,65</t>
+          <t>-55,88; -20,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,34; -21,55</t>
+          <t>-50,67; -11,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,88</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,57</t>
+          <t>-3,12; 1,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,94</t>
+          <t>-3,62; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,32</t>
+          <t>-3,93; 0,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,03</t>
+          <t>-2,03; 2,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,65</t>
+          <t>-2,33; 1,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,43</t>
+          <t>-2,98; 0,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,59</t>
+          <t>-1,77; 1,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,62</t>
+          <t>-2,35; 0,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; -0,2</t>
+          <t>-2,86; -0,06</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-53,35%</t>
+          <t>-51,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-40,61%</t>
+          <t>-33,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-48,17%</t>
+          <t>-44,13%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,93; 81,83</t>
+          <t>-67,52; 68,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,45; 50,24</t>
+          <t>-71,61; 36,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,17; 22,55</t>
+          <t>-80,12; 4,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,13; 187,01</t>
+          <t>-53,81; 153,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,35; 93,71</t>
+          <t>-61,79; 99,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,98; 33,72</t>
+          <t>-69,45; 44,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,61; 72,16</t>
+          <t>-45,91; 68,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,04; 26,96</t>
+          <t>-58,95; 33,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,6; -5,25</t>
+          <t>-68,33; -1,61</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; -0,02</t>
+          <t>-1,77; 0,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,26</t>
+          <t>-2,0; -0,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; -0,81</t>
+          <t>-2,38; -0,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,77</t>
+          <t>-0,8; 0,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,49</t>
+          <t>-1,08; 0,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,5</t>
+          <t>-0,9; 0,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,19</t>
+          <t>-1,02; 0,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; -0,11</t>
+          <t>-1,26; -0,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; -0,36</t>
+          <t>-1,37; -0,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-44,67%</t>
+          <t>-38,71%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,38%</t>
+          <t>-4,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-29,76%</t>
+          <t>-23,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 0,03</t>
+          <t>-41,78; 2,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,8; -8,27</t>
+          <t>-47,23; -6,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -22,67</t>
+          <t>-55,54; -14,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 32,54</t>
+          <t>-25,6; 35,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 22,1</t>
+          <t>-35,85; 18,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 21,41</t>
+          <t>-28,46; 22,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 6,46</t>
+          <t>-28,26; 7,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,44; -3,47</t>
+          <t>-36,25; -4,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,85; -12,42</t>
+          <t>-38,13; -7,5</t>
         </is>
       </c>
     </row>
